--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_15-01-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_15-01-2026.xlsx
@@ -593,7 +593,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>£9.69</t>
+          <t>£9.59</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://www.planetinsulation.co.uk/products/celotex-pir-tb-ga-xr?variant=42844828467437</t>
+          <t>£45.09</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>£20.30</t>
+          <t>£20.15</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>£23.38</t>
+          <t>£23.30</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>£25.10</t>
+          <t>£24.99</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>£32.15</t>
+          <t>£31.99</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>£37.39</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>£37.00</t>
+          <t>£36.18</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>£26.99</t>
+          <t>£26.60</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>£32.99</t>
+          <t>£32.35</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>£87.37</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>£35.99</t>
+          <t>£35.55</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>£40.99</t>
+          <t>£40.40</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
